--- a/DataTables/Datas/quest.xlsx
+++ b/DataTables/Datas/quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7532B1ED-B294-4FD7-8FA5-FFBA28304ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8178CB-B28F-4AF7-B726-66FEAD11CA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/Datas/quest.xlsx
+++ b/DataTables/Datas/quest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8178CB-B28F-4AF7-B726-66FEAD11CA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1D40F7-26FB-402B-A35E-20BC75ABF955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -131,6 +131,14 @@
   </si>
   <si>
     <t>你不知道该干什么，问下前面这个长得像骨裂的人吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳赛继续办！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去想各种办法让拳赛开起来。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,6 +648,29 @@
         <v>29</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H10" s="2"/>
     </row>
